--- a/member_deposit/2026-08-19_会员沉淀分析.xlsx
+++ b/member_deposit/2026-08-19_会员沉淀分析.xlsx
@@ -452,13 +452,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24094</v>
+        <v>24386</v>
       </c>
       <c r="C2" t="n">
-        <v>24056</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>24348</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+292</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>24094</v>
@@ -471,13 +473,15 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25531</v>
+        <v>26014</v>
       </c>
       <c r="C3" t="n">
-        <v>25530</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>26013</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+483</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>25531</v>
@@ -490,13 +494,15 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52074</v>
+        <v>52577</v>
       </c>
       <c r="C4" t="n">
-        <v>52070</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+        <v>52573</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+503</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>52074</v>
@@ -509,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71145</v>
+        <v>71598</v>
       </c>
       <c r="C5" t="n">
-        <v>71108</v>
+        <v>71561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+454</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -530,13 +536,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9510</v>
+        <v>9768</v>
       </c>
       <c r="C6" t="n">
-        <v>9510</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
+        <v>9768</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+258</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>9510</v>
@@ -549,13 +557,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17210</v>
+        <v>17368</v>
       </c>
       <c r="C7" t="n">
-        <v>17210</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>17368</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+158</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>17210</v>
@@ -568,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13174</v>
+        <v>13214</v>
       </c>
       <c r="C8" t="n">
-        <v>13023</v>
+        <v>13063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -589,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>212738</v>
+        <v>214925</v>
       </c>
       <c r="C9" t="n">
-        <v>212507</v>
+        <v>214694</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -684,7 +694,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -702,7 +712,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -720,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -738,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -756,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -792,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -810,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -828,7 +838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -846,7 +856,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -864,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -882,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -900,7 +910,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -918,7 +928,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -936,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -954,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -972,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -990,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1008,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1026,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1044,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1062,7 +1072,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1080,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1098,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1134,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1188,7 +1198,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D30" t="n">
         <v>4</v>
@@ -1206,7 +1216,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
